--- a/.github/workflows/data/reporte_api_productivo.xlsx
+++ b/.github/workflows/data/reporte_api_productivo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Husband\github\iniciativas\.github\workflows\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{422BA0A9-F4FD-46E0-A6D4-E6C7C0931145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED272CB-B450-4603-8902-77B77188F75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3708" yWindow="3084" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>API</t>
   </si>
@@ -55,6 +55,15 @@
   </si>
   <si>
     <t>/accounts/{id}</t>
+  </si>
+  <si>
+    <t>API BS Customer Credit Rating Paid V1</t>
+  </si>
+  <si>
+    <t>POST</t>
+  </si>
+  <si>
+    <t>/customer-credit-rating/initiate</t>
   </si>
 </sst>
 </file>
@@ -390,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.33203125" customWidth="1"/>
@@ -442,6 +451,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/.github/workflows/data/reporte_api_productivo.xlsx
+++ b/.github/workflows/data/reporte_api_productivo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Husband\github\iniciativas\.github\workflows\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED272CB-B450-4603-8902-77B77188F75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA6AEC3-B45C-4002-A7B6-00F5835EBD30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>API</t>
   </si>
@@ -64,6 +64,15 @@
   </si>
   <si>
     <t>/customer-credit-rating/initiate</t>
+  </si>
+  <si>
+    <t>API BS Payment Initiation Credit Card V1</t>
+  </si>
+  <si>
+    <t>PUT</t>
+  </si>
+  <si>
+    <t>/payment-initiations/{id}/quotes/{quoteId}/update</t>
   </si>
 </sst>
 </file>
@@ -399,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.33203125" customWidth="1"/>
@@ -462,6 +471,17 @@
         <v>12</v>
       </c>
     </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
